--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753713755_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23302336</v>
+        <v>4365161</v>
       </c>
       <c r="L2" t="n">
-        <v>13854170</v>
+        <v>2373579</v>
       </c>
       <c r="M2" t="n">
-        <v>3498142</v>
+        <v>518469</v>
       </c>
       <c r="N2" t="n">
-        <v>186786</v>
+        <v>15351</v>
       </c>
       <c r="O2" t="n">
-        <v>2064378</v>
+        <v>299958</v>
       </c>
       <c r="P2" t="n">
-        <v>812485</v>
+        <v>119648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999896287918091</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.919055163860321</v>
+        <v>0.8511297106742859</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8273346424102783</v>
+        <v>0.7003619074821472</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7825159430503845</v>
+        <v>0.6166971325874329</v>
       </c>
       <c r="U2" t="n">
-        <v>0.484403520822525</v>
+        <v>0.1288765370845795</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8327109813690186</v>
+        <v>0.67658531665802</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8904179334640503</v>
+        <v>0.8047295808792114</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23302336</v>
+        <v>4365161</v>
       </c>
       <c r="E3" t="n">
-        <v>1972113</v>
+        <v>675157</v>
       </c>
       <c r="F3" t="n">
-        <v>38774</v>
+        <v>10277</v>
       </c>
       <c r="G3" t="n">
-        <v>3309</v>
+        <v>817</v>
       </c>
       <c r="H3" t="n">
-        <v>1321</v>
+        <v>437</v>
       </c>
       <c r="I3" t="n">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="J3" t="n">
-        <v>50347770</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>54709701</v>
+        <v>10600610</v>
       </c>
       <c r="L3" t="n">
-        <v>62789079</v>
+        <v>12110404</v>
       </c>
       <c r="M3" t="n">
-        <v>76437196</v>
+        <v>15158632</v>
       </c>
       <c r="N3" t="n">
-        <v>81434606</v>
+        <v>16222818</v>
       </c>
       <c r="O3" t="n">
-        <v>79118421</v>
+        <v>15762911</v>
       </c>
       <c r="P3" t="n">
-        <v>81013424</v>
+        <v>16193574</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9203872084617615</v>
+        <v>0.864065945148468</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8447899222373962</v>
+        <v>0.7214306592941284</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7489756941795349</v>
+        <v>0.5544423460960388</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4182587563991547</v>
+        <v>0.1716749221086502</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8105606436729431</v>
+        <v>0.588492214679718</v>
       </c>
       <c r="W3" t="n">
-        <v>0.840572714805603</v>
+        <v>0.6186780333518982</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1944250</v>
+        <v>722792</v>
       </c>
       <c r="E4" t="n">
-        <v>13854170</v>
+        <v>2373579</v>
       </c>
       <c r="F4" t="n">
-        <v>549299</v>
+        <v>172458</v>
       </c>
       <c r="G4" t="n">
-        <v>18207</v>
+        <v>8491</v>
       </c>
       <c r="H4" t="n">
-        <v>31263</v>
+        <v>11824</v>
       </c>
       <c r="I4" t="n">
-        <v>2351</v>
+        <v>955</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>2052329</v>
+        <v>763506</v>
       </c>
       <c r="L4" t="n">
-        <v>2891376</v>
+        <v>1015496</v>
       </c>
       <c r="M4" t="n">
-        <v>972236</v>
+        <v>322250</v>
       </c>
       <c r="N4" t="n">
-        <v>198814</v>
+        <v>103763</v>
       </c>
       <c r="O4" t="n">
-        <v>414727</v>
+        <v>143383</v>
       </c>
       <c r="P4" t="n">
-        <v>99991</v>
+        <v>29033</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999948143959045</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9197206497192383</v>
+        <v>0.8575490713119507</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8359711170196533</v>
+        <v>0.7107402086257935</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7653785943984985</v>
+        <v>0.5839150547981262</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4489076733589172</v>
+        <v>0.1472284942865372</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8214865326881409</v>
+        <v>0.6294716000556946</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8647776246070862</v>
+        <v>0.6995445489883423</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>67295</v>
+        <v>26498</v>
       </c>
       <c r="E5" t="n">
-        <v>811484</v>
+        <v>295917</v>
       </c>
       <c r="F5" t="n">
-        <v>3498142</v>
+        <v>518469</v>
       </c>
       <c r="G5" t="n">
-        <v>74569</v>
+        <v>31310</v>
       </c>
       <c r="H5" t="n">
-        <v>205699</v>
+        <v>57537</v>
       </c>
       <c r="I5" t="n">
-        <v>13373</v>
+        <v>5386</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2015634</v>
+        <v>686723</v>
       </c>
       <c r="L5" t="n">
-        <v>2545375</v>
+        <v>916521</v>
       </c>
       <c r="M5" t="n">
-        <v>1172426</v>
+        <v>416649</v>
       </c>
       <c r="N5" t="n">
-        <v>259794</v>
+        <v>74068</v>
       </c>
       <c r="O5" t="n">
-        <v>482474</v>
+        <v>209748</v>
       </c>
       <c r="P5" t="n">
-        <v>154100</v>
+        <v>73745</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999960064888</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9504390358924866</v>
+        <v>0.9116575717926025</v>
       </c>
       <c r="S5" t="n">
-        <v>0.933762788772583</v>
+        <v>0.8823089003562927</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9738710522651672</v>
+        <v>0.9549890756607056</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9944126605987549</v>
+        <v>0.9891672134399414</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9890691637992859</v>
+        <v>0.9784886240959167</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969043731689453</v>
+        <v>0.993739128112793</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>40382</v>
+        <v>13921</v>
       </c>
       <c r="E6" t="n">
-        <v>63622</v>
+        <v>20201</v>
       </c>
       <c r="F6" t="n">
-        <v>114224</v>
+        <v>30237</v>
       </c>
       <c r="G6" t="n">
-        <v>186786</v>
+        <v>15351</v>
       </c>
       <c r="H6" t="n">
-        <v>38276</v>
+        <v>8901</v>
       </c>
       <c r="I6" t="n">
-        <v>3244</v>
+        <v>799</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>342</v>
+        <v>277</v>
       </c>
       <c r="E7" t="n">
-        <v>42110</v>
+        <v>23119</v>
       </c>
       <c r="F7" t="n">
-        <v>261277</v>
+        <v>104648</v>
       </c>
       <c r="G7" t="n">
-        <v>97777</v>
+        <v>59844</v>
       </c>
       <c r="H7" t="n">
-        <v>2064378</v>
+        <v>299958</v>
       </c>
       <c r="I7" t="n">
-        <v>80907</v>
+        <v>21858</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>2047</v>
+        <v>1102</v>
       </c>
       <c r="F8" t="n">
-        <v>8662</v>
+        <v>4630</v>
       </c>
       <c r="G8" t="n">
-        <v>4952</v>
+        <v>3301</v>
       </c>
       <c r="H8" t="n">
-        <v>138168</v>
+        <v>64684</v>
       </c>
       <c r="I8" t="n">
-        <v>812485</v>
+        <v>119648</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
